--- a/wwwroot/files/engineering_score.xlsx
+++ b/wwwroot/files/engineering_score.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kriangkrai\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HOME\WEB\WebENG\WebENG\wwwroot\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -830,10 +830,10 @@
     <t>Manpower</t>
   </si>
   <si>
-    <t>% participation</t>
-  </si>
-  <si>
     <t>Remaining Cost</t>
+  </si>
+  <si>
+    <t>% Participation</t>
   </si>
 </sst>
 </file>
@@ -4311,6 +4311,15 @@
     <xf numFmtId="165" fontId="8" fillId="6" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="6" borderId="43" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -4322,15 +4331,6 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -5234,7 +5234,7 @@
       <c r="S1" s="492" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="725" t="s">
+      <c r="T1" s="728" t="s">
         <v>91</v>
       </c>
       <c r="U1" s="493"/>
@@ -5325,7 +5325,7 @@
       <c r="S2" s="480" t="s">
         <v>11</v>
       </c>
-      <c r="T2" s="726"/>
+      <c r="T2" s="729"/>
       <c r="U2" s="147">
         <f>SUM(U3:U42)</f>
         <v>0</v>
@@ -10024,7 +10024,7 @@
       <c r="S1" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="727" t="s">
+      <c r="T1" s="730" t="s">
         <v>91</v>
       </c>
       <c r="U1" s="67"/>
@@ -10120,7 +10120,7 @@
       <c r="S2" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="T2" s="728"/>
+      <c r="T2" s="731"/>
       <c r="U2" s="13">
         <f>SUM(U3:U44)</f>
         <v>120810207.25</v>
@@ -13963,61 +13963,61 @@
   <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.140625" style="730" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" style="729" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="729" customWidth="1"/>
-    <col min="4" max="4" width="37.5703125" style="730" customWidth="1"/>
-    <col min="5" max="5" width="35.7109375" style="730" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" style="729" customWidth="1"/>
-    <col min="7" max="7" width="16" style="729" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" style="729" customWidth="1"/>
-    <col min="9" max="9" width="18" style="729" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="729" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="729" customWidth="1"/>
-    <col min="12" max="12" width="18.42578125" style="729" customWidth="1"/>
-    <col min="13" max="13" width="19.5703125" style="729" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="729"/>
+    <col min="1" max="1" width="33.140625" style="725" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" style="725" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="725" customWidth="1"/>
+    <col min="4" max="4" width="37.5703125" style="726" customWidth="1"/>
+    <col min="5" max="5" width="35.7109375" style="726" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" style="725" customWidth="1"/>
+    <col min="7" max="7" width="16" style="725" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" style="725" customWidth="1"/>
+    <col min="9" max="9" width="18" style="725" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="725" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="725" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" style="725" customWidth="1"/>
+    <col min="13" max="13" width="19.5703125" style="725" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="725"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="731" t="s">
+      <c r="A1" s="727" t="s">
         <v>252</v>
       </c>
-      <c r="B1" s="731" t="s">
+      <c r="B1" s="727" t="s">
         <v>253</v>
       </c>
-      <c r="C1" s="731" t="s">
+      <c r="C1" s="727" t="s">
         <v>254</v>
       </c>
-      <c r="D1" s="731" t="s">
+      <c r="D1" s="727" t="s">
         <v>255</v>
       </c>
-      <c r="E1" s="731" t="s">
+      <c r="E1" s="727" t="s">
         <v>251</v>
       </c>
-      <c r="F1" s="731" t="s">
+      <c r="F1" s="727" t="s">
         <v>256</v>
       </c>
-      <c r="G1" s="731" t="s">
+      <c r="G1" s="727" t="s">
         <v>257</v>
       </c>
-      <c r="H1" s="731" t="s">
+      <c r="H1" s="727" t="s">
         <v>258</v>
       </c>
-      <c r="I1" s="731" t="s">
+      <c r="I1" s="727" t="s">
         <v>259</v>
       </c>
-      <c r="J1" s="731" t="s">
+      <c r="J1" s="727" t="s">
         <v>260</v>
       </c>
-      <c r="K1" s="731" t="s">
+      <c r="K1" s="727" t="s">
         <v>261</v>
       </c>
-      <c r="L1" s="731" t="s">
+      <c r="L1" s="727" t="s">
+        <v>263</v>
+      </c>
+      <c r="M1" s="727" t="s">
         <v>262</v>
-      </c>
-      <c r="M1" s="731" t="s">
-        <v>263</v>
       </c>
     </row>
   </sheetData>

--- a/wwwroot/files/engineering_score.xlsx
+++ b/wwwroot/files/engineering_score.xlsx
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JoB Backlog2013-2017'!$A$2:$AL$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'JobBacklog2013-2016'!$A$1:$AR$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Sheet1!$A$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Sheet1!$A$1:$N$1</definedName>
     <definedName name="B">#N/A</definedName>
     <definedName name="PeriodInPlan">#REF!=MEDIAN(#REF!,#REF!,#REF!+#REF!-1)</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'JoB Backlog2013-2017'!$A$1:$AD$31</definedName>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="265">
   <si>
     <t>No.</t>
   </si>
@@ -834,6 +834,9 @@
   </si>
   <si>
     <t>% Participation</t>
+  </si>
+  <si>
+    <t>Finished Date</t>
   </si>
 </sst>
 </file>
@@ -1013,7 +1016,7 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1098,6 +1101,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="88">
     <border>
@@ -2219,7 +2228,7 @@
     <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="732">
+  <cellXfs count="734">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4331,6 +4340,12 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -13960,7 +13975,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" style="725" customWidth="1"/>
@@ -13976,10 +13991,11 @@
     <col min="11" max="11" width="15.7109375" style="725" customWidth="1"/>
     <col min="12" max="12" width="18.42578125" style="725" customWidth="1"/>
     <col min="13" max="13" width="19.5703125" style="725" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="725"/>
+    <col min="14" max="14" width="15.5703125" style="733" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="725"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="727" t="s">
         <v>252</v>
       </c>
@@ -14019,9 +14035,13 @@
       <c r="M1" s="727" t="s">
         <v>262</v>
       </c>
+      <c r="N1" s="732" t="s">
+        <v>264</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1"/>
+  <autoFilter ref="A1:N1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>